--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="194">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -593,6 +593,10 @@
   </si>
   <si>
     <t>fr-lm-device-use.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
   </si>
   <si>
     <t>localisation anatomique</t>
@@ -3998,13 +4002,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>131</v>
+        <v>186</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4034,7 +4038,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4072,10 +4076,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4098,13 +4102,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4155,7 +4159,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4172,10 +4176,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4201,10 +4205,10 @@
         <v>150</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4255,7 +4259,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-device-use.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-device-use.header.langue</t>
+    <t>fr-lm-device-use.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,7 +451,7 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-device-use.usageStatus</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="191">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,13 +422,16 @@
 </t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Status de l'utilisation du DM (ex active, completed, etc).</t>
+  </si>
+  <si>
+    <t>Statut</t>
+  </si>
+  <si>
+    <t>Valeur issue du http://hl7.org/fhir/ValueSet/device-statement-status</t>
+  </si>
+  <si>
+    <t>https://hl7.org/fhir/R4/valueset-device-statement-status.html</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -454,15 +457,6 @@
     <t>fr-lm-entry.header.language</t>
   </si>
   <si>
-    <t>fr-lm-device-use.usageStatus</t>
-  </si>
-  <si>
-    <t>Status de l'utilisation du DM (ex active, completed, etc).</t>
-  </si>
-  <si>
-    <t>https://hl7.org/fhir/R4/valueset-device-statement-status.html</t>
-  </si>
-  <si>
     <t>fr-lm-device-use.periodOfUse</t>
   </si>
   <si>
@@ -581,9 +575,6 @@
   </si>
   <si>
     <t>Durée d'utilisation</t>
-  </si>
-  <si>
-    <t>fr-lm-device-use.DeviceUsageStatus</t>
   </si>
   <si>
     <t>fr-lm-device-use.device</t>
@@ -924,7 +915,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ33"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="50.0390625" customWidth="true" bestFit="true"/>
@@ -951,8 +942,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.3203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.94140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2608,7 +2599,7 @@
         <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2638,10 +2629,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2659,10 +2650,10 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2676,10 +2667,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2705,10 +2696,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2759,7 +2750,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2776,10 +2767,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2805,10 +2796,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2859,7 +2850,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2876,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2902,13 +2893,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2937,9 +2928,11 @@
       <c r="X20" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Y20" s="2"/>
+      <c r="Y20" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -2957,7 +2950,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2969,15 +2962,15 @@
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>73</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2985,7 +2978,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -3000,13 +2993,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3057,10 +3050,10 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -3069,26 +3062,26 @@
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>73</v>
+        <v>153</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>73</v>
@@ -3100,15 +3093,17 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>73</v>
@@ -3145,50 +3140,50 @@
         <v>73</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>73</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>73</v>
@@ -3200,16 +3195,16 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3247,39 +3242,39 @@
         <v>73</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>162</v>
+        <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3287,7 +3282,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>79</v>
@@ -3302,17 +3297,15 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>73</v>
@@ -3361,10 +3354,10 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>79</v>
@@ -3373,15 +3366,15 @@
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>73</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3404,13 +3397,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3473,7 +3466,7 @@
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>175</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26">
@@ -3689,7 +3682,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>79</v>
@@ -3704,7 +3697,7 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>181</v>
@@ -3764,7 +3757,7 @@
         <v>180</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>79</v>
@@ -3789,7 +3782,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>79</v>
@@ -3804,13 +3797,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3839,9 +3832,11 @@
       <c r="X29" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Y29" s="2"/>
+      <c r="Y29" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>73</v>
@@ -3862,7 +3857,7 @@
         <v>182</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>79</v>
@@ -3876,10 +3871,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3887,10 +3882,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -3902,13 +3897,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>103</v>
+        <v>187</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3959,13 +3954,13 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>73</v>
@@ -3976,10 +3971,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4002,13 +3997,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4038,7 +4033,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>188</v>
+        <v>73</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4059,7 +4054,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4071,206 +4066,6 @@
         <v>73</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
